--- a/04_DESIGN_TABLES/DesignTable_6600_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6600_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,32 +2913,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6600-32-32-32-FG</t>
+          <t>6600-24-24-24-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="C10" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="E10" t="n">
         <v>0.125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="G10" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2947,28 +2947,28 @@
         <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="M10" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="O10" t="n">
         <v>0.125</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="T10" t="n">
         <v>60</v>
@@ -2977,91 +2977,91 @@
         <v>37</v>
       </c>
       <c r="V10" t="n">
-        <v>3.38</v>
+        <v>2.59</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.0785</v>
+        <v>0.776</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.3936</v>
+        <v>1.0504</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.4242</v>
+        <v>1.1134</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.862</v>
+        <v>0.7063</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66277</v>
+        <v>1.29904</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.702</v>
+        <v>0.5295</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.325</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.4202</v>
+        <v>1.065</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.198</v>
+        <v>0.8885</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.1175</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.862</v>
+        <v>0.7063</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.78</v>
+        <v>1.312</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.38</v>
+        <v>2.59</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AW10" t="n">
         <v>0.08333</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="AY10" t="n">
         <v>0.04511</v>
@@ -3073,13 +3073,13 @@
         <v>0.08333</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="BC10" t="n">
         <v>0.08333</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="BE10" t="n">
         <v>0.04511</v>
@@ -3091,79 +3091,343 @@
         <v>0.08333</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.40978</v>
+        <v>1.78478</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.7399</v>
+        <v>0.5674</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.08333</v>
       </c>
       <c r="BK10" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>6600-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Female Swivel Branch Tee, 1 7/8-12 JIC x 1 7/8-12 JIC x 1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] Air-Way s193 only (double-pass 20 rows) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): D3@BORE: Brennan TFA catalog p57 table TFA-p057-t01 (MJ-MJ-FJS TEE) row 6600-24-24-24-FG column 'A3 DRILL' = 1.312 (catalog_verified.json); Air-Way s193 printed ".31" (garbled, cell left empty; Q-GARBLE) - consistent with 1.31, the siblings D1 / D2 1.31; OMi Items row 2080: no ID; no own STEP; equals the 2026-10-02 proposal | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; ASSUMED for a tee); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>D (3) printed ".31" on Air-Way (siblings 1.31); copied as printed | D (3): printed ".31" (not a clean decimal) -&gt; left empty, MISSING | BRENNAN-ONLY (2026-10-18) for D3 only (Brennan 1.312 = Air-Way '.31' read as 1.31). Kept Air-Way where Brennan differs: M10@DRIVE Air-Way 1.86 vs Brennan M4 LGTH 1.870</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>6600-24-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6600-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="T11" t="n">
+        <v>60</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.20489</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="AH11" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="BL11" t="n">
         <v>1.25</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BM11" t="n">
         <v>3.38</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BN11" t="n">
         <v>2.5</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BO11" t="n">
         <v>1.727</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BP11" t="n">
         <v>1.727</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BQ11" t="n">
         <v>2.5</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="BR11" t="n">
         <v>1.71</v>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>6600-32-32-32-FG</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>Female Swivel Branch Tee, 2 1/2-12 JIC x 2 1/2-12 JIC x 2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>6600</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>Air-Way s193 only (double-pass 20 rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; ASSUMED for a tee); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>6600-32-32-32-FG</t>
         </is>
